--- a/reports/pdf_rolling5_20260703.xlsx
+++ b/reports/pdf_rolling5_20260703.xlsx
@@ -570,7 +570,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 6,036억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 16종목  /  매도 9종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,341억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 16종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -666,10 +666,10 @@
         <v>59</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2496682350</v>
+        <v>2544649350</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.414</v>
+        <v>0.476</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         <v>-87</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-7924612500</v>
+        <v>-8076862500</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>-1.313</v>
+        <v>-1.512</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         <v>52</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>552687720</v>
+        <v>563306120</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.092</v>
+        <v>0.105</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         <v>-67</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-7044447000</v>
+        <v>-7179787000</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>-1.167</v>
+        <v>-1.344</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
         <v>33</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1460002500</v>
+        <v>1488052500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.242</v>
+        <v>0.279</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -765,10 +765,10 @@
         <v>-49</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2601459000</v>
+        <v>-2651439000</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>-0.431</v>
+        <v>-0.496</v>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2894708700</v>
+        <v>2950322700</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.48</v>
+        <v>0.552</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
         <v>-36</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-504426960</v>
+        <v>-514118160</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.096</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         <v>31</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>531503370</v>
+        <v>541714770</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
         <v>-33</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-4946832000</v>
+        <v>-5041872000</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>-0.819</v>
+        <v>-0.944</v>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         <v>28</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1275225000</v>
+        <v>1299725000</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0.211</v>
+        <v>0.243</v>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         <v>-24</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2171109600</v>
+        <v>-2212821600</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>-0.36</v>
+        <v>-0.414</v>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
         <v>27</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1086335550</v>
+        <v>1107206550</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.18</v>
+        <v>0.207</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         <v>-19</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1700994000</v>
+        <v>-1733674000</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>-0.282</v>
+        <v>-0.325</v>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         <v>15</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2054934000</v>
+        <v>2094414000</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.34</v>
+        <v>0.392</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
         <v>-6</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2979342000</v>
+        <v>-3036582000</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>-0.494</v>
+        <v>-0.569</v>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
         <v>14</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1890247800</v>
+        <v>1926563800</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.313</v>
+        <v>0.361</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
         <v>-3</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-768258000</v>
+        <v>-783018000</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>-0.127</v>
+        <v>-0.147</v>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>531326400</v>
+        <v>541534400</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1464687000</v>
+        <v>1492827000</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.243</v>
+        <v>0.28</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         <v>9</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>3377524500</v>
+        <v>3442414500</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.645</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1654149000</v>
+        <v>1685929000</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.274</v>
+        <v>0.316</v>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>429100200</v>
+        <v>437344200</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
@@ -1156,10 +1156,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>451273500</v>
+        <v>459943500</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.075</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1463646000</v>
+        <v>1491766000</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.242</v>
+        <v>0.279</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,954억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 3종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,858억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 3종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1297,10 +1297,10 @@
         <v>493</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>12251050000</v>
+        <v>12445168750</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>2.473</v>
+        <v>2.562</v>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
@@ -1316,10 +1316,10 @@
         <v>-20</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1781248000</v>
+        <v>-1809472000</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>-0.36</v>
+        <v>-0.372</v>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         <v>68</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>447265920</v>
+        <v>454352880</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
         <v>6</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1485888000</v>
+        <v>1509432000</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.3</v>
+        <v>0.311</v>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,774억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 3종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,365억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 3종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1478,10 +1478,10 @@
         <v>40</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1335250000</v>
+        <v>1345750000</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.354</v>
+        <v>0.4</v>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         <v>-60</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-4106466000</v>
+        <v>-4138758000</v>
       </c>
       <c r="J33" s="16" t="n">
-        <v>-1.088</v>
+        <v>-1.23</v>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1100780100</v>
+        <v>2532163200</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.292</v>
+        <v>0.752</v>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>99→120</t>
+          <t>19→40</t>
         </is>
       </c>
       <c r="G34" s="17" t="n"/>
@@ -1537,21 +1537,21 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>2512406400</v>
+        <v>1109436300</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.666</v>
+        <v>0.33</v>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>19→40</t>
+          <t>99→120</t>
         </is>
       </c>
       <c r="G35" s="17" t="n"/>
@@ -1563,7 +1563,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,898억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,838억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1659,10 +1659,10 @@
         <v>170</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2908062500</v>
+        <v>2960125000</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>1.004</v>
+        <v>1.043</v>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         <v>-5</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-345253000</v>
+        <v>-351434000</v>
       </c>
       <c r="J40" s="16" t="n">
-        <v>-0.119</v>
+        <v>-0.124</v>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 394억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 16종목  /  매도 14종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 355억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 16종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -1788,10 +1788,10 @@
         <v>110</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>131566600</v>
+        <v>119680000</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.334</v>
+        <v>0.337</v>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
@@ -1807,10 +1807,10 @@
         <v>-111</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-245970450</v>
+        <v>-216672000</v>
       </c>
       <c r="J45" s="16" t="n">
-        <v>-0.624</v>
+        <v>-0.61</v>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
         <v>80</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>68572000</v>
+        <v>63808000</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.174</v>
+        <v>0.18</v>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
@@ -1847,10 +1847,10 @@
         <v>-110</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-346296500</v>
+        <v>-336160000</v>
       </c>
       <c r="J46" s="16" t="n">
-        <v>-0.878</v>
+        <v>-0.946</v>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
@@ -1868,10 +1868,10 @@
         <v>29</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>111113500</v>
+        <v>106256000</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.282</v>
+        <v>0.299</v>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         <v>-76</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-40226800</v>
+        <v>-40432000</v>
       </c>
       <c r="J47" s="16" t="n">
-        <v>-0.102</v>
+        <v>-0.114</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         <v>27</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>48952350</v>
+        <v>42012000</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.124</v>
+        <v>0.118</v>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
@@ -1927,10 +1927,10 @@
         <v>-50</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-81765000</v>
+        <v>-72280000</v>
       </c>
       <c r="J48" s="16" t="n">
-        <v>-0.207</v>
+        <v>-0.203</v>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
         <v>25</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>327060000</v>
+        <v>263200000</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.829</v>
+        <v>0.741</v>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         <v>-32</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-46312960</v>
+        <v>-45209600</v>
       </c>
       <c r="J49" s="16" t="n">
-        <v>-0.117</v>
+        <v>-0.127</v>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
@@ -1988,10 +1988,10 @@
         <v>23</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>102660500</v>
+        <v>93288000</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.26</v>
+        <v>0.263</v>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-24442600</v>
+        <v>-67984000</v>
       </c>
       <c r="J50" s="16" t="n">
-        <v>-0.062</v>
+        <v>-0.191</v>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -2028,10 +2028,10 @@
         <v>19</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>84656400</v>
+        <v>78736000</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.215</v>
+        <v>0.222</v>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-72000600</v>
+        <v>-23833600</v>
       </c>
       <c r="J51" s="16" t="n">
-        <v>-0.183</v>
+        <v>-0.067</v>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -2068,10 +2068,10 @@
         <v>12</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>63516000</v>
+        <v>53952000</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.161</v>
+        <v>0.152</v>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
@@ -2087,10 +2087,10 @@
         <v>-17</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-64464000</v>
+        <v>-65144000</v>
       </c>
       <c r="J52" s="16" t="n">
-        <v>-0.163</v>
+        <v>-0.183</v>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         <v>11</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>26591400</v>
+        <v>19272000</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.067</v>
+        <v>0.054</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
         <v>-15</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-42126750</v>
+        <v>-41940000</v>
       </c>
       <c r="J53" s="16" t="n">
-        <v>-0.107</v>
+        <v>-0.118</v>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         <v>9</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>121367700</v>
+        <v>110952000</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.308</v>
+        <v>0.312</v>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         <v>-14</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-295855000</v>
+        <v>-297360000</v>
       </c>
       <c r="J54" s="16" t="n">
-        <v>-0.75</v>
+        <v>-0.837</v>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         <v>8</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>133668000</v>
+        <v>117120000</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.339</v>
+        <v>0.33</v>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-76574700</v>
+        <v>-61920000</v>
       </c>
       <c r="J55" s="16" t="n">
-        <v>-0.194</v>
+        <v>-0.174</v>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
         <v>7</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>53253900</v>
+        <v>47152000</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.135</v>
+        <v>0.133</v>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
         <v>-9</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-118381500</v>
+        <v>-101304000</v>
       </c>
       <c r="J56" s="16" t="n">
-        <v>-0.3</v>
+        <v>-0.285</v>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>21843500</v>
+        <v>19460000</v>
       </c>
       <c r="D57" s="12" t="n">
         <v>0.055</v>
@@ -2287,10 +2287,10 @@
         <v>-4</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-49706800</v>
+        <v>-39904000</v>
       </c>
       <c r="J57" s="16" t="n">
-        <v>-0.126</v>
+        <v>-0.112</v>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>파마리서치  (신규)</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>115814000</v>
+        <v>97120000</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.294</v>
+        <v>0.273</v>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>0→4</t>
+          <t>22→26</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2327,10 +2327,10 @@
         <v>-3</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-22041000</v>
+        <v>-20904000</v>
       </c>
       <c r="J58" s="16" t="n">
-        <v>-0.056</v>
+        <v>-0.059</v>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파마리서치  (신규)</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>67308000</v>
+        <v>115360000</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.171</v>
+        <v>0.325</v>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>68→72</t>
+          <t>0→4</t>
         </is>
       </c>
       <c r="G59" s="17" t="n"/>
@@ -2367,21 +2367,21 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>106966000</v>
+        <v>56896000</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.271</v>
+        <v>0.16</v>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>22→26</t>
+          <t>68→72</t>
         </is>
       </c>
       <c r="G60" s="17" t="n"/>
@@ -2393,7 +2393,7 @@
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 639억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 5종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B62" s="4" t="n"/>
@@ -2489,10 +2489,10 @@
         <v>184</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>893550000</v>
+        <v>909650000</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>1.399</v>
+        <v>1.438</v>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
@@ -2508,10 +2508,10 @@
         <v>-622</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-812624340</v>
+        <v>-827266220</v>
       </c>
       <c r="J65" s="16" t="n">
-        <v>-1.273</v>
+        <v>-1.308</v>
       </c>
       <c r="K65" s="13" t="inlineStr">
         <is>
@@ -2529,10 +2529,10 @@
         <v>44</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>423442800</v>
+        <v>431072400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.663</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
@@ -2548,10 +2548,10 @@
         <v>-214</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-489332400</v>
+        <v>-498149200</v>
       </c>
       <c r="J66" s="16" t="n">
-        <v>-0.766</v>
+        <v>-0.788</v>
       </c>
       <c r="K66" s="13" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
         <v>32</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>1280496000</v>
+        <v>1303568000</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>2.005</v>
+        <v>2.061</v>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
@@ -2588,10 +2588,10 @@
         <v>-136</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-606859200</v>
+        <v>-617793600</v>
       </c>
       <c r="J67" s="16" t="n">
-        <v>-0.95</v>
+        <v>-0.977</v>
       </c>
       <c r="K67" s="13" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
         <v>13</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>629148000</v>
+        <v>640484000</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.985</v>
+        <v>1.013</v>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         <v>-17</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-663280500</v>
+        <v>-675231500</v>
       </c>
       <c r="J68" s="16" t="n">
-        <v>-1.039</v>
+        <v>-1.068</v>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
@@ -2649,10 +2649,10 @@
         <v>9</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>177921900</v>
+        <v>181127700</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.279</v>
+        <v>0.286</v>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260703.xlsx
+++ b/reports/pdf_rolling5_20260703.xlsx
@@ -2000,21 +2000,21 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-67984000</v>
+        <v>-23833600</v>
       </c>
       <c r="J50" s="16" t="n">
-        <v>-0.191</v>
+        <v>-0.067</v>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -2040,21 +2040,21 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-23833600</v>
+        <v>-67984000</v>
       </c>
       <c r="J51" s="16" t="n">
-        <v>-0.067</v>
+        <v>-0.191</v>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -2200,21 +2200,21 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-61920000</v>
+        <v>-101304000</v>
       </c>
       <c r="J55" s="16" t="n">
-        <v>-0.174</v>
+        <v>-0.285</v>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>140→131</t>
+          <t>116→107</t>
         </is>
       </c>
     </row>
@@ -2240,21 +2240,21 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-101304000</v>
+        <v>-61920000</v>
       </c>
       <c r="J56" s="16" t="n">
-        <v>-0.285</v>
+        <v>-0.174</v>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>116→107</t>
+          <t>140→131</t>
         </is>
       </c>
     </row>
@@ -2301,21 +2301,21 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>97120000</v>
+        <v>56896000</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.273</v>
+        <v>0.16</v>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>22→26</t>
+          <t>68→72</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2341,21 +2341,21 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>파마리서치  (신규)</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>115360000</v>
+        <v>97120000</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.325</v>
+        <v>0.273</v>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>0→4</t>
+          <t>22→26</t>
         </is>
       </c>
       <c r="G59" s="17" t="n"/>
@@ -2367,21 +2367,21 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파마리서치  (신규)</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>56896000</v>
+        <v>115360000</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.16</v>
+        <v>0.325</v>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>68→72</t>
+          <t>0→4</t>
         </is>
       </c>
       <c r="G60" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260703.xlsx
+++ b/reports/pdf_rolling5_20260703.xlsx
@@ -1511,21 +1511,21 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2532163200</v>
+        <v>1109436300</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.752</v>
+        <v>0.33</v>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>19→40</t>
+          <t>99→120</t>
         </is>
       </c>
       <c r="G34" s="17" t="n"/>
@@ -1537,21 +1537,21 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1109436300</v>
+        <v>2532163200</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.33</v>
+        <v>0.752</v>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>99→120</t>
+          <t>19→40</t>
         </is>
       </c>
       <c r="G35" s="17" t="n"/>
@@ -2301,21 +2301,21 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파마리서치  (신규)</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>56896000</v>
+        <v>115360000</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.16</v>
+        <v>0.325</v>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>68→72</t>
+          <t>0→4</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2367,21 +2367,21 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>파마리서치  (신규)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>115360000</v>
+        <v>56896000</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.325</v>
+        <v>0.16</v>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>0→4</t>
+          <t>68→72</t>
         </is>
       </c>
       <c r="G60" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260703.xlsx
+++ b/reports/pdf_rolling5_20260703.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
-    <numFmt numFmtId="165" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;;0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -154,7 +153,7 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,7 +163,7 @@
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -570,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,341억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 16종목  /  매도 9종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      오늘 2026-07-03  vs  5일전 2026-06-26      매수 16종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,11 +664,15 @@
       <c r="B6" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>2544649350</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>0.476</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -684,11 +687,15 @@
       <c r="H6" s="15" t="n">
         <v>-87</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <v>-8076862500</v>
-      </c>
-      <c r="J6" s="16" t="n">
-        <v>-1.512</v>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -705,11 +712,15 @@
       <c r="B7" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>563306120</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0.105</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -724,11 +735,15 @@
       <c r="H7" s="15" t="n">
         <v>-67</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <v>-7179787000</v>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>-1.344</v>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -745,11 +760,15 @@
       <c r="B8" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>1488052500</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>0.279</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -764,11 +783,15 @@
       <c r="H8" s="15" t="n">
         <v>-49</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <v>-2651439000</v>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>-0.496</v>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -785,11 +808,15 @@
       <c r="B9" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>2950322700</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0.552</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -804,11 +831,15 @@
       <c r="H9" s="15" t="n">
         <v>-36</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <v>-514118160</v>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>-0.096</v>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -825,11 +856,15 @@
       <c r="B10" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>541714770</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>0.101</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -844,11 +879,15 @@
       <c r="H10" s="15" t="n">
         <v>-33</v>
       </c>
-      <c r="I10" s="15" t="n">
-        <v>-5041872000</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>-0.944</v>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -865,11 +904,15 @@
       <c r="B11" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>1299725000</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>0.243</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -884,11 +927,15 @@
       <c r="H11" s="15" t="n">
         <v>-24</v>
       </c>
-      <c r="I11" s="15" t="n">
-        <v>-2212821600</v>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>-0.414</v>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -905,11 +952,15 @@
       <c r="B12" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>1107206550</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>0.207</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -924,11 +975,15 @@
       <c r="H12" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I12" s="15" t="n">
-        <v>-1733674000</v>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>-0.325</v>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -945,11 +1000,15 @@
       <c r="B13" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>2094414000</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>0.392</v>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -964,11 +1023,15 @@
       <c r="H13" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I13" s="15" t="n">
-        <v>-3036582000</v>
-      </c>
-      <c r="J13" s="16" t="n">
-        <v>-0.569</v>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
@@ -985,11 +1048,15 @@
       <c r="B14" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>1926563800</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>0.361</v>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -1004,11 +1071,15 @@
       <c r="H14" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>-783018000</v>
-      </c>
-      <c r="J14" s="16" t="n">
-        <v>-0.147</v>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -1025,11 +1096,15 @@
       <c r="B15" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>541534400</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>0.101</v>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -1051,11 +1126,15 @@
       <c r="B16" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>1492827000</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>0.28</v>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
@@ -1077,11 +1156,15 @@
       <c r="B17" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>3442414500</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>0.645</v>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -1103,11 +1186,15 @@
       <c r="B18" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>1685929000</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>0.316</v>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
@@ -1129,11 +1216,15 @@
       <c r="B19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>437344200</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>0.082</v>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
@@ -1155,11 +1246,15 @@
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>459943500</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>0.08599999999999999</v>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
@@ -1181,11 +1276,15 @@
       <c r="B21" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>1491766000</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>0.279</v>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -1201,7 +1300,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,858억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 3종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      오늘 2026-07-03  vs  5일전 2026-06-26      매수 3종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1296,11 +1395,15 @@
       <c r="B26" s="11" t="n">
         <v>493</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>12445168750</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>2.562</v>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
@@ -1315,11 +1418,15 @@
       <c r="H26" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I26" s="15" t="n">
-        <v>-1809472000</v>
-      </c>
-      <c r="J26" s="16" t="n">
-        <v>-0.372</v>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
@@ -1336,11 +1443,15 @@
       <c r="B27" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>454352880</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>0.094</v>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
@@ -1362,11 +1473,15 @@
       <c r="B28" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>1509432000</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>0.311</v>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
@@ -1382,7 +1497,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,365억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 3종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      오늘 2026-07-03  vs  5일전 2026-06-26      매수 3종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1477,11 +1592,15 @@
       <c r="B33" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>1345750000</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>0.4</v>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
@@ -1496,11 +1615,15 @@
       <c r="H33" s="15" t="n">
         <v>-60</v>
       </c>
-      <c r="I33" s="15" t="n">
-        <v>-4138758000</v>
-      </c>
-      <c r="J33" s="16" t="n">
-        <v>-1.23</v>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
@@ -1517,11 +1640,15 @@
       <c r="B34" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>1109436300</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>0.33</v>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
@@ -1543,11 +1670,15 @@
       <c r="B35" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>2532163200</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>0.752</v>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
@@ -1563,7 +1694,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,838억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      오늘 2026-07-03  vs  5일전 2026-06-26      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1658,11 +1789,15 @@
       <c r="B40" s="11" t="n">
         <v>170</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>2960125000</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>1.043</v>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
@@ -1677,11 +1812,15 @@
       <c r="H40" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I40" s="15" t="n">
-        <v>-351434000</v>
-      </c>
-      <c r="J40" s="16" t="n">
-        <v>-0.124</v>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
@@ -1692,7 +1831,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 355억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 16종목  /  매도 14종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      오늘 2026-07-03  vs  5일전 2026-06-26      매수 16종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -1787,11 +1926,15 @@
       <c r="B45" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>119680000</v>
-      </c>
-      <c r="D45" s="12" t="n">
-        <v>0.337</v>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
@@ -1806,11 +1949,15 @@
       <c r="H45" s="15" t="n">
         <v>-111</v>
       </c>
-      <c r="I45" s="15" t="n">
-        <v>-216672000</v>
-      </c>
-      <c r="J45" s="16" t="n">
-        <v>-0.61</v>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
@@ -1827,11 +1974,15 @@
       <c r="B46" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>63808000</v>
-      </c>
-      <c r="D46" s="12" t="n">
-        <v>0.18</v>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
@@ -1846,11 +1997,15 @@
       <c r="H46" s="15" t="n">
         <v>-110</v>
       </c>
-      <c r="I46" s="15" t="n">
-        <v>-336160000</v>
-      </c>
-      <c r="J46" s="16" t="n">
-        <v>-0.946</v>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
@@ -1867,11 +2022,15 @@
       <c r="B47" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>106256000</v>
-      </c>
-      <c r="D47" s="12" t="n">
-        <v>0.299</v>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
@@ -1886,11 +2045,15 @@
       <c r="H47" s="15" t="n">
         <v>-76</v>
       </c>
-      <c r="I47" s="15" t="n">
-        <v>-40432000</v>
-      </c>
-      <c r="J47" s="16" t="n">
-        <v>-0.114</v>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -1907,11 +2070,15 @@
       <c r="B48" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>42012000</v>
-      </c>
-      <c r="D48" s="12" t="n">
-        <v>0.118</v>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
@@ -1926,11 +2093,15 @@
       <c r="H48" s="15" t="n">
         <v>-50</v>
       </c>
-      <c r="I48" s="15" t="n">
-        <v>-72280000</v>
-      </c>
-      <c r="J48" s="16" t="n">
-        <v>-0.203</v>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
@@ -1947,11 +2118,15 @@
       <c r="B49" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>263200000</v>
-      </c>
-      <c r="D49" s="12" t="n">
-        <v>0.741</v>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
@@ -1966,11 +2141,15 @@
       <c r="H49" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I49" s="15" t="n">
-        <v>-45209600</v>
-      </c>
-      <c r="J49" s="16" t="n">
-        <v>-0.127</v>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
@@ -1987,11 +2166,15 @@
       <c r="B50" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>93288000</v>
-      </c>
-      <c r="D50" s="12" t="n">
-        <v>0.263</v>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
@@ -2000,21 +2183,25 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="I50" s="15" t="n">
-        <v>-23833600</v>
-      </c>
-      <c r="J50" s="16" t="n">
-        <v>-0.067</v>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -2027,11 +2214,15 @@
       <c r="B51" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>78736000</v>
-      </c>
-      <c r="D51" s="12" t="n">
-        <v>0.222</v>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
@@ -2040,21 +2231,25 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="I51" s="15" t="n">
-        <v>-67984000</v>
-      </c>
-      <c r="J51" s="16" t="n">
-        <v>-0.191</v>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -2067,11 +2262,15 @@
       <c r="B52" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C52" s="11" t="n">
-        <v>53952000</v>
-      </c>
-      <c r="D52" s="12" t="n">
-        <v>0.152</v>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
@@ -2086,11 +2285,15 @@
       <c r="H52" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I52" s="15" t="n">
-        <v>-65144000</v>
-      </c>
-      <c r="J52" s="16" t="n">
-        <v>-0.183</v>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
@@ -2107,11 +2310,15 @@
       <c r="B53" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C53" s="11" t="n">
-        <v>19272000</v>
-      </c>
-      <c r="D53" s="12" t="n">
-        <v>0.054</v>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
@@ -2126,11 +2333,15 @@
       <c r="H53" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I53" s="15" t="n">
-        <v>-41940000</v>
-      </c>
-      <c r="J53" s="16" t="n">
-        <v>-0.118</v>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
@@ -2147,11 +2358,15 @@
       <c r="B54" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>110952000</v>
-      </c>
-      <c r="D54" s="12" t="n">
-        <v>0.312</v>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
@@ -2166,11 +2381,15 @@
       <c r="H54" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I54" s="15" t="n">
-        <v>-297360000</v>
-      </c>
-      <c r="J54" s="16" t="n">
-        <v>-0.837</v>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
@@ -2187,11 +2406,15 @@
       <c r="B55" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C55" s="11" t="n">
-        <v>117120000</v>
-      </c>
-      <c r="D55" s="12" t="n">
-        <v>0.33</v>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
@@ -2206,11 +2429,15 @@
       <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I55" s="15" t="n">
-        <v>-101304000</v>
-      </c>
-      <c r="J55" s="16" t="n">
-        <v>-0.285</v>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
@@ -2227,11 +2454,15 @@
       <c r="B56" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C56" s="11" t="n">
-        <v>47152000</v>
-      </c>
-      <c r="D56" s="12" t="n">
-        <v>0.133</v>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
@@ -2246,11 +2477,15 @@
       <c r="H56" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I56" s="15" t="n">
-        <v>-61920000</v>
-      </c>
-      <c r="J56" s="16" t="n">
-        <v>-0.174</v>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
@@ -2267,11 +2502,15 @@
       <c r="B57" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C57" s="11" t="n">
-        <v>19460000</v>
-      </c>
-      <c r="D57" s="12" t="n">
-        <v>0.055</v>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
@@ -2286,11 +2525,15 @@
       <c r="H57" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I57" s="15" t="n">
-        <v>-39904000</v>
-      </c>
-      <c r="J57" s="16" t="n">
-        <v>-0.112</v>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
@@ -2307,11 +2550,15 @@
       <c r="B58" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C58" s="11" t="n">
-        <v>115360000</v>
-      </c>
-      <c r="D58" s="12" t="n">
-        <v>0.325</v>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
@@ -2326,11 +2573,15 @@
       <c r="H58" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I58" s="15" t="n">
-        <v>-20904000</v>
-      </c>
-      <c r="J58" s="16" t="n">
-        <v>-0.059</v>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
@@ -2347,11 +2598,15 @@
       <c r="B59" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>97120000</v>
-      </c>
-      <c r="D59" s="12" t="n">
-        <v>0.273</v>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
@@ -2373,11 +2628,15 @@
       <c r="B60" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C60" s="11" t="n">
-        <v>56896000</v>
-      </c>
-      <c r="D60" s="12" t="n">
-        <v>0.16</v>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
@@ -2393,7 +2652,7 @@
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      오늘 2026-07-03  vs  5일전 2026-06-26      매수 5종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      오늘 2026-07-03  vs  5일전 2026-06-26      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B62" s="4" t="n"/>
@@ -2488,11 +2747,15 @@
       <c r="B65" s="11" t="n">
         <v>184</v>
       </c>
-      <c r="C65" s="11" t="n">
-        <v>909650000</v>
-      </c>
-      <c r="D65" s="12" t="n">
-        <v>1.438</v>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
@@ -2507,11 +2770,15 @@
       <c r="H65" s="15" t="n">
         <v>-622</v>
       </c>
-      <c r="I65" s="15" t="n">
-        <v>-827266220</v>
-      </c>
-      <c r="J65" s="16" t="n">
-        <v>-1.308</v>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
         <is>
@@ -2528,11 +2795,15 @@
       <c r="B66" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>431072400</v>
-      </c>
-      <c r="D66" s="12" t="n">
-        <v>0.6820000000000001</v>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
@@ -2547,11 +2818,15 @@
       <c r="H66" s="15" t="n">
         <v>-214</v>
       </c>
-      <c r="I66" s="15" t="n">
-        <v>-498149200</v>
-      </c>
-      <c r="J66" s="16" t="n">
-        <v>-0.788</v>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
         <is>
@@ -2568,11 +2843,15 @@
       <c r="B67" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>1303568000</v>
-      </c>
-      <c r="D67" s="12" t="n">
-        <v>2.061</v>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
@@ -2587,11 +2866,15 @@
       <c r="H67" s="15" t="n">
         <v>-136</v>
       </c>
-      <c r="I67" s="15" t="n">
-        <v>-617793600</v>
-      </c>
-      <c r="J67" s="16" t="n">
-        <v>-0.977</v>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
         <is>
@@ -2608,11 +2891,15 @@
       <c r="B68" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>640484000</v>
-      </c>
-      <c r="D68" s="12" t="n">
-        <v>1.013</v>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
@@ -2627,11 +2914,15 @@
       <c r="H68" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I68" s="15" t="n">
-        <v>-675231500</v>
-      </c>
-      <c r="J68" s="16" t="n">
-        <v>-1.068</v>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
@@ -2648,11 +2939,15 @@
       <c r="B69" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C69" s="11" t="n">
-        <v>181127700</v>
-      </c>
-      <c r="D69" s="12" t="n">
-        <v>0.286</v>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
